--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70C02E48-DEA9-43C0-8F1D-748B5D99AFD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E153898-5C28-4568-8EF3-411FE83B26E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="58">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2442,25 +2442,47 @@
       <c r="N38" s="17"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+      <c r="A39" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B39" s="14">
+        <v>420</v>
+      </c>
+      <c r="C39" s="14">
+        <v>0</v>
+      </c>
+      <c r="D39" s="14">
+        <v>200</v>
+      </c>
+      <c r="E39" s="14">
+        <v>40</v>
+      </c>
+      <c r="F39" s="14">
+        <v>0</v>
+      </c>
+      <c r="G39" s="14">
+        <v>0</v>
+      </c>
+      <c r="H39" s="14">
+        <v>90</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>750</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
+        <v>690</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N39" s="17"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E153898-5C28-4568-8EF3-411FE83B26E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CB96307-319B-4237-83D8-5F002CF5EF6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="58">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2486,25 +2486,47 @@
       <c r="N39" s="17"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+      <c r="A40" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B40" s="14">
+        <v>420</v>
+      </c>
+      <c r="C40" s="14">
+        <v>0</v>
+      </c>
+      <c r="D40" s="14">
+        <v>240</v>
+      </c>
+      <c r="E40" s="14">
+        <v>60</v>
+      </c>
+      <c r="F40" s="14">
+        <v>0</v>
+      </c>
+      <c r="G40" s="14">
+        <v>0</v>
+      </c>
+      <c r="H40" s="14">
+        <v>90</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>810</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
+        <v>630</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N40" s="17"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CB96307-319B-4237-83D8-5F002CF5EF6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C2DAB26-167F-4D14-89AE-A4EF58C58641}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="58">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2530,25 +2530,47 @@
       <c r="N40" s="17"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+      <c r="A41" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B41" s="14">
+        <v>420</v>
+      </c>
+      <c r="C41" s="14">
+        <v>0</v>
+      </c>
+      <c r="D41" s="14">
+        <v>180</v>
+      </c>
+      <c r="E41" s="14">
+        <v>60</v>
+      </c>
+      <c r="F41" s="14">
+        <v>250</v>
+      </c>
+      <c r="G41" s="14">
+        <v>0</v>
+      </c>
+      <c r="H41" s="14">
+        <v>60</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>970</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
+        <v>470</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N41" s="17"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C2DAB26-167F-4D14-89AE-A4EF58C58641}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F7F9295-C6E0-4DBC-BBAE-DC22983A4DF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="58">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2549,7 +2549,7 @@
         <v>250</v>
       </c>
       <c r="G41" s="14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H41" s="14">
         <v>60</v>
@@ -2574,25 +2574,47 @@
       <c r="N41" s="17"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
+      <c r="A42" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B42" s="14">
+        <v>420</v>
+      </c>
+      <c r="C42" s="14">
+        <v>0</v>
+      </c>
+      <c r="D42" s="14">
+        <v>180</v>
+      </c>
+      <c r="E42" s="14">
+        <v>60</v>
+      </c>
+      <c r="F42" s="14">
+        <v>350</v>
+      </c>
+      <c r="G42" s="14">
+        <v>7</v>
+      </c>
+      <c r="H42" s="14">
+        <v>60</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
+        <v>370</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N42" s="17"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F7F9295-C6E0-4DBC-BBAE-DC22983A4DF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7A80C99-3154-4587-844D-C69A24051467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="58">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2618,25 +2618,47 @@
       <c r="N42" s="17"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+      <c r="A43" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B43" s="14">
+        <v>420</v>
+      </c>
+      <c r="C43" s="14">
+        <v>0</v>
+      </c>
+      <c r="D43" s="14">
+        <v>180</v>
+      </c>
+      <c r="E43" s="14">
+        <v>40</v>
+      </c>
+      <c r="F43" s="14">
+        <v>300</v>
+      </c>
+      <c r="G43" s="14">
+        <v>6</v>
+      </c>
+      <c r="H43" s="14">
+        <v>60</v>
+      </c>
+      <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+        <v>1000</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
+        <v>440</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N43" s="17"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7A80C99-3154-4587-844D-C69A24051467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC299787-E0F6-419E-AF8A-F23BA86859B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="58">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2662,25 +2662,47 @@
       <c r="N43" s="17"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
+      <c r="A44" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B44" s="14">
+        <v>380</v>
+      </c>
+      <c r="C44" s="14">
+        <v>0</v>
+      </c>
+      <c r="D44" s="14">
+        <v>180</v>
+      </c>
+      <c r="E44" s="14">
+        <v>30</v>
+      </c>
+      <c r="F44" s="14">
+        <v>200</v>
+      </c>
+      <c r="G44" s="14">
+        <v>4</v>
+      </c>
+      <c r="H44" s="14">
+        <v>60</v>
+      </c>
+      <c r="I44" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
+        <v>850</v>
+      </c>
+      <c r="J44" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
+        <v>590</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N44" s="17"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC299787-E0F6-419E-AF8A-F23BA86859B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A1F020A-6C34-4D81-ABF1-DF7A82FB3FB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="58">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2706,47 +2706,91 @@
       <c r="N44" s="17"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
+      <c r="A45" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B45" s="14">
+        <v>420</v>
+      </c>
+      <c r="C45" s="14">
+        <v>0</v>
+      </c>
+      <c r="D45" s="14">
+        <v>240</v>
+      </c>
+      <c r="E45" s="14">
+        <v>40</v>
+      </c>
+      <c r="F45" s="14">
+        <v>250</v>
+      </c>
+      <c r="G45" s="14">
+        <v>5</v>
+      </c>
+      <c r="H45" s="14">
+        <v>60</v>
+      </c>
+      <c r="I45" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J45" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
+        <v>430</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N45" s="17"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
+      <c r="A46" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B46" s="14">
+        <v>420</v>
+      </c>
+      <c r="C46" s="14">
+        <v>0</v>
+      </c>
+      <c r="D46" s="14">
+        <v>240</v>
+      </c>
+      <c r="E46" s="14">
+        <v>50</v>
+      </c>
+      <c r="F46" s="14">
+        <v>0</v>
+      </c>
+      <c r="G46" s="14">
+        <v>0</v>
+      </c>
+      <c r="H46" s="14">
+        <v>90</v>
+      </c>
+      <c r="I46" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
+        <v>800</v>
+      </c>
+      <c r="J46" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
+        <v>640</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N46" s="17"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A1F020A-6C34-4D81-ABF1-DF7A82FB3FB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3256B2AF-57D1-4DBD-AFC4-941D1C6EC9E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="58">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2794,25 +2794,47 @@
       <c r="N46" s="17"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15" t="str">
+      <c r="A47" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B47" s="14">
+        <v>420</v>
+      </c>
+      <c r="C47" s="14">
+        <v>0</v>
+      </c>
+      <c r="D47" s="14">
+        <v>240</v>
+      </c>
+      <c r="E47" s="14">
+        <v>60</v>
+      </c>
+      <c r="F47" s="14">
+        <v>0</v>
+      </c>
+      <c r="G47" s="14">
+        <v>0</v>
+      </c>
+      <c r="H47" s="14">
+        <v>90</v>
+      </c>
+      <c r="I47" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
+        <v>810</v>
+      </c>
+      <c r="J47" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
+        <v>630</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N47" s="17"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3256B2AF-57D1-4DBD-AFC4-941D1C6EC9E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD4AFDA3-6B72-4A8C-8913-ED7DDDE2E51A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="58">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2838,25 +2838,47 @@
       <c r="N47" s="17"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="13"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="15" t="str">
+      <c r="A48" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B48" s="14">
+        <v>420</v>
+      </c>
+      <c r="C48" s="14">
+        <v>0</v>
+      </c>
+      <c r="D48" s="14">
+        <v>240</v>
+      </c>
+      <c r="E48" s="14">
+        <v>40</v>
+      </c>
+      <c r="F48" s="14">
+        <v>250</v>
+      </c>
+      <c r="G48" s="14">
+        <v>5</v>
+      </c>
+      <c r="H48" s="14">
+        <v>90</v>
+      </c>
+      <c r="I48" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J48" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
+        <v>400</v>
+      </c>
+      <c r="K48" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N48" s="17"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD4AFDA3-6B72-4A8C-8913-ED7DDDE2E51A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5227DAA-9586-4B02-901A-084E3B1320C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="58">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2882,25 +2882,47 @@
       <c r="N48" s="17"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="13"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="15" t="str">
+      <c r="A49" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B49" s="14">
+        <v>420</v>
+      </c>
+      <c r="C49" s="14">
+        <v>0</v>
+      </c>
+      <c r="D49" s="14">
+        <v>180</v>
+      </c>
+      <c r="E49" s="14">
+        <v>60</v>
+      </c>
+      <c r="F49" s="14">
+        <v>350</v>
+      </c>
+      <c r="G49" s="14">
+        <v>7</v>
+      </c>
+      <c r="H49" s="14">
+        <v>60</v>
+      </c>
+      <c r="I49" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="15" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J49" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
+        <v>370</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N49" s="17"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5227DAA-9586-4B02-901A-084E3B1320C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FD9C8D7-FB99-4636-8602-FCB9E37DE859}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="58">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2926,25 +2926,47 @@
       <c r="N49" s="17"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="13"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="15" t="str">
+      <c r="A50" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B50" s="14">
+        <v>420</v>
+      </c>
+      <c r="C50" s="14">
+        <v>0</v>
+      </c>
+      <c r="D50" s="14">
+        <v>180</v>
+      </c>
+      <c r="E50" s="14">
+        <v>40</v>
+      </c>
+      <c r="F50" s="14">
+        <v>300</v>
+      </c>
+      <c r="G50" s="14">
+        <v>6</v>
+      </c>
+      <c r="H50" s="14">
+        <v>90</v>
+      </c>
+      <c r="I50" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="15" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J50" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
+        <v>410</v>
+      </c>
+      <c r="K50" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N50" s="17"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FD9C8D7-FB99-4636-8602-FCB9E37DE859}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CF94B79-964F-4DE4-8FC2-6CFEFE3AFD76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="58">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2970,25 +2970,47 @@
       <c r="N50" s="17"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="13"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="15" t="str">
+      <c r="A51" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B51" s="14">
+        <v>420</v>
+      </c>
+      <c r="C51" s="14">
+        <v>0</v>
+      </c>
+      <c r="D51" s="14">
+        <v>180</v>
+      </c>
+      <c r="E51" s="14">
+        <v>40</v>
+      </c>
+      <c r="F51" s="14">
+        <v>200</v>
+      </c>
+      <c r="G51" s="14">
+        <v>4</v>
+      </c>
+      <c r="H51" s="14">
+        <v>90</v>
+      </c>
+      <c r="I51" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J51" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
+        <v>510</v>
+      </c>
+      <c r="K51" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N51" s="17"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CF94B79-964F-4DE4-8FC2-6CFEFE3AFD76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD1164CA-5832-47A2-9269-391E6D620138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="58">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3014,25 +3014,47 @@
       <c r="N51" s="17"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="13"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="15" t="str">
+      <c r="A52" s="13">
+        <v>46290</v>
+      </c>
+      <c r="B52" s="14">
+        <v>420</v>
+      </c>
+      <c r="C52" s="14">
+        <v>0</v>
+      </c>
+      <c r="D52" s="14">
+        <v>180</v>
+      </c>
+      <c r="E52" s="14">
+        <v>60</v>
+      </c>
+      <c r="F52" s="14">
+        <v>250</v>
+      </c>
+      <c r="G52" s="14">
+        <v>5</v>
+      </c>
+      <c r="H52" s="14">
+        <v>90</v>
+      </c>
+      <c r="I52" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="15" t="str">
+        <v>1000</v>
+      </c>
+      <c r="J52" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
+        <v>440</v>
+      </c>
+      <c r="K52" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L52" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M52" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N52" s="17"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD1164CA-5832-47A2-9269-391E6D620138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DF1A27E-9618-433B-BC58-E3C049ED3AFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="58">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3058,25 +3058,47 @@
       <c r="N52" s="17"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="13"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="15" t="str">
+      <c r="A53" s="13">
+        <v>46291</v>
+      </c>
+      <c r="B53" s="14">
+        <v>420</v>
+      </c>
+      <c r="C53" s="14">
+        <v>0</v>
+      </c>
+      <c r="D53" s="14">
+        <v>240</v>
+      </c>
+      <c r="E53" s="14">
+        <v>60</v>
+      </c>
+      <c r="F53" s="14">
+        <v>0</v>
+      </c>
+      <c r="G53" s="14">
+        <v>0</v>
+      </c>
+      <c r="H53" s="14">
+        <v>90</v>
+      </c>
+      <c r="I53" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="15" t="str">
+        <v>810</v>
+      </c>
+      <c r="J53" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="16"/>
+        <v>630</v>
+      </c>
+      <c r="K53" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L53" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M53" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N53" s="17"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DF1A27E-9618-433B-BC58-E3C049ED3AFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C08D5CC-4EAA-428D-A9B4-AE79EC4F5A4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="59">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -209,6 +209,9 @@
   </si>
   <si>
     <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>Stressed</t>
   </si>
 </sst>
 </file>
@@ -3102,47 +3105,91 @@
       <c r="N53" s="17"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="13"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="15" t="str">
+      <c r="A54" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B54" s="14">
+        <v>120</v>
+      </c>
+      <c r="C54" s="14">
+        <v>0</v>
+      </c>
+      <c r="D54" s="14">
+        <v>60</v>
+      </c>
+      <c r="E54" s="14">
+        <v>0</v>
+      </c>
+      <c r="F54" s="14">
+        <v>0</v>
+      </c>
+      <c r="G54" s="14">
+        <v>0</v>
+      </c>
+      <c r="H54" s="14">
+        <v>60</v>
+      </c>
+      <c r="I54" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="15" t="str">
+        <v>240</v>
+      </c>
+      <c r="J54" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="16"/>
+        <v>1200</v>
+      </c>
+      <c r="K54" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L54" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M54" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N54" s="17"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A55" s="13"/>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="15" t="str">
+      <c r="A55" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B55" s="14">
+        <v>240</v>
+      </c>
+      <c r="C55" s="14">
+        <v>0</v>
+      </c>
+      <c r="D55" s="14">
+        <v>60</v>
+      </c>
+      <c r="E55" s="14">
+        <v>0</v>
+      </c>
+      <c r="F55" s="14">
+        <v>0</v>
+      </c>
+      <c r="G55" s="14">
+        <v>0</v>
+      </c>
+      <c r="H55" s="14">
+        <v>60</v>
+      </c>
+      <c r="I55" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="15" t="str">
+        <v>360</v>
+      </c>
+      <c r="J55" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="16"/>
-      <c r="L55" s="16"/>
-      <c r="M55" s="16"/>
+        <v>1080</v>
+      </c>
+      <c r="K55" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="L55" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M55" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N55" s="17"/>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C08D5CC-4EAA-428D-A9B4-AE79EC4F5A4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8527DD4E-E05B-4C46-9FC7-EF36C8F1DDCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="59">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3193,25 +3193,47 @@
       <c r="N55" s="17"/>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" s="13"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="15" t="str">
+      <c r="A56" s="13">
+        <v>46294</v>
+      </c>
+      <c r="B56" s="14">
+        <v>420</v>
+      </c>
+      <c r="C56" s="14">
+        <v>0</v>
+      </c>
+      <c r="D56" s="14">
+        <v>180</v>
+      </c>
+      <c r="E56" s="14">
+        <v>40</v>
+      </c>
+      <c r="F56" s="14">
+        <v>0</v>
+      </c>
+      <c r="G56" s="14">
+        <v>0</v>
+      </c>
+      <c r="H56" s="14">
+        <v>90</v>
+      </c>
+      <c r="I56" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="15" t="str">
+        <v>730</v>
+      </c>
+      <c r="J56" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="16"/>
-      <c r="L56" s="16"/>
-      <c r="M56" s="16"/>
+        <v>710</v>
+      </c>
+      <c r="K56" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L56" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M56" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N56" s="17"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8527DD4E-E05B-4C46-9FC7-EF36C8F1DDCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8A63C45-AE7E-4300-98AD-73034623E84D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="59">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3237,25 +3237,47 @@
       <c r="N56" s="17"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A57" s="13"/>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="15" t="str">
+      <c r="A57" s="13">
+        <v>46295</v>
+      </c>
+      <c r="B57" s="14">
+        <v>420</v>
+      </c>
+      <c r="C57" s="14">
+        <v>0</v>
+      </c>
+      <c r="D57" s="14">
+        <v>180</v>
+      </c>
+      <c r="E57" s="14">
+        <v>40</v>
+      </c>
+      <c r="F57" s="14">
+        <v>0</v>
+      </c>
+      <c r="G57" s="14">
+        <v>0</v>
+      </c>
+      <c r="H57" s="14">
+        <v>90</v>
+      </c>
+      <c r="I57" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="15" t="str">
+        <v>730</v>
+      </c>
+      <c r="J57" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="16"/>
+        <v>710</v>
+      </c>
+      <c r="K57" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L57" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M57" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N57" s="17"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8A63C45-AE7E-4300-98AD-73034623E84D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97A1636A-5D03-4D7B-88D6-8B44E92DA295}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="59">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3281,25 +3281,47 @@
       <c r="N57" s="17"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A58" s="13"/>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-      <c r="I58" s="15" t="str">
+      <c r="A58" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B58" s="14">
+        <v>420</v>
+      </c>
+      <c r="C58" s="14">
+        <v>0</v>
+      </c>
+      <c r="D58" s="14">
+        <v>180</v>
+      </c>
+      <c r="E58" s="14">
+        <v>60</v>
+      </c>
+      <c r="F58" s="14">
+        <v>0</v>
+      </c>
+      <c r="G58" s="14">
+        <v>0</v>
+      </c>
+      <c r="H58" s="14">
+        <v>90</v>
+      </c>
+      <c r="I58" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="15" t="str">
+        <v>750</v>
+      </c>
+      <c r="J58" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K58" s="16"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="16"/>
+        <v>690</v>
+      </c>
+      <c r="K58" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L58" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M58" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N58" s="17"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97A1636A-5D03-4D7B-88D6-8B44E92DA295}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{765B6970-6DA6-42B2-AE6F-37B74B928095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="59">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3325,25 +3325,47 @@
       <c r="N58" s="17"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A59" s="13"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14"/>
-      <c r="I59" s="15" t="str">
+      <c r="A59" s="13">
+        <v>46297</v>
+      </c>
+      <c r="B59" s="14">
+        <v>420</v>
+      </c>
+      <c r="C59" s="14">
+        <v>0</v>
+      </c>
+      <c r="D59" s="14">
+        <v>180</v>
+      </c>
+      <c r="E59" s="14">
+        <v>60</v>
+      </c>
+      <c r="F59" s="14">
+        <v>0</v>
+      </c>
+      <c r="G59" s="14">
+        <v>0</v>
+      </c>
+      <c r="H59" s="14">
+        <v>90</v>
+      </c>
+      <c r="I59" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J59" s="15" t="str">
+        <v>750</v>
+      </c>
+      <c r="J59" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K59" s="16"/>
-      <c r="L59" s="16"/>
-      <c r="M59" s="16"/>
+        <v>690</v>
+      </c>
+      <c r="K59" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L59" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M59" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N59" s="17"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{765B6970-6DA6-42B2-AE6F-37B74B928095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABB373C1-74F8-46BA-9271-1200A0E28920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="59">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3369,25 +3369,47 @@
       <c r="N59" s="17"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A60" s="13"/>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
-      <c r="I60" s="15" t="str">
+      <c r="A60" s="13">
+        <v>46298</v>
+      </c>
+      <c r="B60" s="14">
+        <v>420</v>
+      </c>
+      <c r="C60" s="14">
+        <v>0</v>
+      </c>
+      <c r="D60" s="14">
+        <v>180</v>
+      </c>
+      <c r="E60" s="14">
+        <v>90</v>
+      </c>
+      <c r="F60" s="14">
+        <v>0</v>
+      </c>
+      <c r="G60" s="14">
+        <v>0</v>
+      </c>
+      <c r="H60" s="14">
+        <v>90</v>
+      </c>
+      <c r="I60" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J60" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J60" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K60" s="16"/>
-      <c r="L60" s="16"/>
-      <c r="M60" s="16"/>
+        <v>660</v>
+      </c>
+      <c r="K60" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L60" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M60" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N60" s="17"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABB373C1-74F8-46BA-9271-1200A0E28920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD5082E1-E404-47B4-8690-C20C39660830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="59">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3413,25 +3413,47 @@
       <c r="N60" s="17"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A61" s="13"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
-      <c r="I61" s="15" t="str">
+      <c r="A61" s="13">
+        <v>46299</v>
+      </c>
+      <c r="B61" s="14">
+        <v>420</v>
+      </c>
+      <c r="C61" s="14">
+        <v>0</v>
+      </c>
+      <c r="D61" s="14">
+        <v>180</v>
+      </c>
+      <c r="E61" s="14">
+        <v>60</v>
+      </c>
+      <c r="F61" s="14">
+        <v>0</v>
+      </c>
+      <c r="G61" s="14">
+        <v>0</v>
+      </c>
+      <c r="H61" s="14">
+        <v>90</v>
+      </c>
+      <c r="I61" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J61" s="15" t="str">
+        <v>750</v>
+      </c>
+      <c r="J61" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K61" s="16"/>
-      <c r="L61" s="16"/>
-      <c r="M61" s="16"/>
+        <v>690</v>
+      </c>
+      <c r="K61" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L61" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M61" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N61" s="17"/>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD5082E1-E404-47B4-8690-C20C39660830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E86FEA6-5184-4E5C-8665-E923586DB376}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="59">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3457,25 +3457,47 @@
       <c r="N61" s="17"/>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A62" s="13"/>
-      <c r="B62" s="14"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14"/>
-      <c r="I62" s="15" t="str">
+      <c r="A62" s="13">
+        <v>46300</v>
+      </c>
+      <c r="B62" s="14">
+        <v>420</v>
+      </c>
+      <c r="C62" s="14">
+        <v>0</v>
+      </c>
+      <c r="D62" s="14">
+        <v>180</v>
+      </c>
+      <c r="E62" s="14">
+        <v>40</v>
+      </c>
+      <c r="F62" s="14">
+        <v>250</v>
+      </c>
+      <c r="G62" s="14">
+        <v>5</v>
+      </c>
+      <c r="H62" s="14">
+        <v>60</v>
+      </c>
+      <c r="I62" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J62" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J62" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K62" s="16"/>
-      <c r="L62" s="16"/>
-      <c r="M62" s="16"/>
+        <v>490</v>
+      </c>
+      <c r="K62" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L62" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M62" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N62" s="17"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E86FEA6-5184-4E5C-8665-E923586DB376}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87181168-B86A-417A-954E-6F0A022AFB8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="59">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3501,25 +3501,47 @@
       <c r="N62" s="17"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A63" s="13"/>
-      <c r="B63" s="14"/>
-      <c r="C63" s="14"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
-      <c r="H63" s="14"/>
-      <c r="I63" s="15" t="str">
+      <c r="A63" s="13">
+        <v>46301</v>
+      </c>
+      <c r="B63" s="14">
+        <v>420</v>
+      </c>
+      <c r="C63" s="14">
+        <v>0</v>
+      </c>
+      <c r="D63" s="14">
+        <v>180</v>
+      </c>
+      <c r="E63" s="14">
+        <v>60</v>
+      </c>
+      <c r="F63" s="14">
+        <v>350</v>
+      </c>
+      <c r="G63" s="14">
+        <v>7</v>
+      </c>
+      <c r="H63" s="14">
+        <v>90</v>
+      </c>
+      <c r="I63" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J63" s="15" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J63" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K63" s="16"/>
-      <c r="L63" s="16"/>
-      <c r="M63" s="16"/>
+        <v>340</v>
+      </c>
+      <c r="K63" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L63" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M63" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N63" s="17"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87181168-B86A-417A-954E-6F0A022AFB8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D527C6E9-C093-4159-A181-36ADC9202C6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="59">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3545,25 +3545,47 @@
       <c r="N63" s="17"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A64" s="13"/>
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
-      <c r="H64" s="14"/>
-      <c r="I64" s="15" t="str">
+      <c r="A64" s="13">
+        <v>46302</v>
+      </c>
+      <c r="B64" s="14">
+        <v>420</v>
+      </c>
+      <c r="C64" s="14">
+        <v>0</v>
+      </c>
+      <c r="D64" s="14">
+        <v>180</v>
+      </c>
+      <c r="E64" s="14">
+        <v>40</v>
+      </c>
+      <c r="F64" s="14">
+        <v>300</v>
+      </c>
+      <c r="G64" s="14">
+        <v>6</v>
+      </c>
+      <c r="H64" s="14">
+        <v>90</v>
+      </c>
+      <c r="I64" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J64" s="15" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J64" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K64" s="16"/>
-      <c r="L64" s="16"/>
-      <c r="M64" s="16"/>
+        <v>410</v>
+      </c>
+      <c r="K64" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L64" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M64" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N64" s="17"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D527C6E9-C093-4159-A181-36ADC9202C6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{543D37D2-B4E3-4613-B7C0-E34031945427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="59">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3589,25 +3589,47 @@
       <c r="N64" s="17"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A65" s="13"/>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
-      <c r="H65" s="14"/>
-      <c r="I65" s="15" t="str">
+      <c r="A65" s="13">
+        <v>46303</v>
+      </c>
+      <c r="B65" s="14">
+        <v>420</v>
+      </c>
+      <c r="C65" s="14">
+        <v>0</v>
+      </c>
+      <c r="D65" s="14">
+        <v>180</v>
+      </c>
+      <c r="E65" s="14">
+        <v>60</v>
+      </c>
+      <c r="F65" s="14">
+        <v>200</v>
+      </c>
+      <c r="G65" s="14">
+        <v>4</v>
+      </c>
+      <c r="H65" s="14">
+        <v>90</v>
+      </c>
+      <c r="I65" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J65" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J65" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K65" s="16"/>
-      <c r="L65" s="16"/>
-      <c r="M65" s="16"/>
+        <v>490</v>
+      </c>
+      <c r="K65" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L65" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M65" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N65" s="17"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{543D37D2-B4E3-4613-B7C0-E34031945427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E506BEBC-1E7E-478C-925A-1F91562C6653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="59">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3633,47 +3633,91 @@
       <c r="N65" s="17"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A66" s="13"/>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14"/>
-      <c r="H66" s="14"/>
-      <c r="I66" s="15" t="str">
+      <c r="A66" s="13">
+        <v>46304</v>
+      </c>
+      <c r="B66" s="14">
+        <v>420</v>
+      </c>
+      <c r="C66" s="14">
+        <v>0</v>
+      </c>
+      <c r="D66" s="14">
+        <v>180</v>
+      </c>
+      <c r="E66" s="14">
+        <v>60</v>
+      </c>
+      <c r="F66" s="14">
+        <v>0</v>
+      </c>
+      <c r="G66" s="14">
+        <v>0</v>
+      </c>
+      <c r="H66" s="14">
+        <v>90</v>
+      </c>
+      <c r="I66" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J66" s="15" t="str">
+        <v>750</v>
+      </c>
+      <c r="J66" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K66" s="16"/>
-      <c r="L66" s="16"/>
-      <c r="M66" s="16"/>
+        <v>690</v>
+      </c>
+      <c r="K66" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L66" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M66" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N66" s="17"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A67" s="13"/>
-      <c r="B67" s="14"/>
-      <c r="C67" s="14"/>
-      <c r="D67" s="14"/>
-      <c r="E67" s="14"/>
-      <c r="F67" s="14"/>
-      <c r="G67" s="14"/>
-      <c r="H67" s="14"/>
-      <c r="I67" s="15" t="str">
+      <c r="A67" s="13">
+        <v>46305</v>
+      </c>
+      <c r="B67" s="14">
+        <v>420</v>
+      </c>
+      <c r="C67" s="14">
+        <v>0</v>
+      </c>
+      <c r="D67" s="14">
+        <v>180</v>
+      </c>
+      <c r="E67" s="14">
+        <v>60</v>
+      </c>
+      <c r="F67" s="14">
+        <v>0</v>
+      </c>
+      <c r="G67" s="14">
+        <v>0</v>
+      </c>
+      <c r="H67" s="14">
+        <v>90</v>
+      </c>
+      <c r="I67" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J67" s="15" t="str">
+        <v>750</v>
+      </c>
+      <c r="J67" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K67" s="16"/>
-      <c r="L67" s="16"/>
-      <c r="M67" s="16"/>
+        <v>690</v>
+      </c>
+      <c r="K67" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L67" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M67" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N67" s="17"/>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E506BEBC-1E7E-478C-925A-1F91562C6653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5266C44-8A39-4958-B891-6B780DC86DA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="59">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3721,25 +3721,47 @@
       <c r="N67" s="17"/>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A68" s="13"/>
-      <c r="B68" s="14"/>
-      <c r="C68" s="14"/>
-      <c r="D68" s="14"/>
-      <c r="E68" s="14"/>
-      <c r="F68" s="14"/>
-      <c r="G68" s="14"/>
-      <c r="H68" s="14"/>
-      <c r="I68" s="15" t="str">
+      <c r="A68" s="13">
+        <v>46306</v>
+      </c>
+      <c r="B68" s="14">
+        <v>420</v>
+      </c>
+      <c r="C68" s="14">
+        <v>0</v>
+      </c>
+      <c r="D68" s="14">
+        <v>240</v>
+      </c>
+      <c r="E68" s="14">
+        <v>40</v>
+      </c>
+      <c r="F68" s="14">
+        <v>0</v>
+      </c>
+      <c r="G68" s="14">
+        <v>0</v>
+      </c>
+      <c r="H68" s="14">
+        <v>90</v>
+      </c>
+      <c r="I68" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J68" s="15" t="str">
+        <v>790</v>
+      </c>
+      <c r="J68" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K68" s="16"/>
-      <c r="L68" s="16"/>
-      <c r="M68" s="16"/>
+        <v>650</v>
+      </c>
+      <c r="K68" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L68" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M68" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N68" s="17"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5266C44-8A39-4958-B891-6B780DC86DA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6C296FC-B915-48CC-9682-535143446E25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="59">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3765,25 +3765,47 @@
       <c r="N68" s="17"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A69" s="13"/>
-      <c r="B69" s="14"/>
-      <c r="C69" s="14"/>
-      <c r="D69" s="14"/>
-      <c r="E69" s="14"/>
-      <c r="F69" s="14"/>
-      <c r="G69" s="14"/>
-      <c r="H69" s="14"/>
-      <c r="I69" s="15" t="str">
+      <c r="A69" s="13">
+        <v>46307</v>
+      </c>
+      <c r="B69" s="14">
+        <v>420</v>
+      </c>
+      <c r="C69" s="14">
+        <v>0</v>
+      </c>
+      <c r="D69" s="14">
+        <v>300</v>
+      </c>
+      <c r="E69" s="14">
+        <v>20</v>
+      </c>
+      <c r="F69" s="14">
+        <v>0</v>
+      </c>
+      <c r="G69" s="14">
+        <v>0</v>
+      </c>
+      <c r="H69" s="14">
+        <v>90</v>
+      </c>
+      <c r="I69" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J69" s="15" t="str">
+        <v>830</v>
+      </c>
+      <c r="J69" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K69" s="16"/>
-      <c r="L69" s="16"/>
-      <c r="M69" s="16"/>
+        <v>610</v>
+      </c>
+      <c r="K69" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L69" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M69" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N69" s="17"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6C296FC-B915-48CC-9682-535143446E25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C15796D-79FD-41FA-A83B-3BEA543AA5BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="59">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3809,25 +3809,47 @@
       <c r="N69" s="17"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A70" s="13"/>
-      <c r="B70" s="14"/>
-      <c r="C70" s="14"/>
-      <c r="D70" s="14"/>
-      <c r="E70" s="14"/>
-      <c r="F70" s="14"/>
-      <c r="G70" s="14"/>
-      <c r="H70" s="14"/>
-      <c r="I70" s="15" t="str">
+      <c r="A70" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B70" s="14">
+        <v>420</v>
+      </c>
+      <c r="C70" s="14">
+        <v>0</v>
+      </c>
+      <c r="D70" s="14">
+        <v>300</v>
+      </c>
+      <c r="E70" s="14">
+        <v>0</v>
+      </c>
+      <c r="F70" s="14">
+        <v>0</v>
+      </c>
+      <c r="G70" s="14">
+        <v>0</v>
+      </c>
+      <c r="H70" s="14">
+        <v>15</v>
+      </c>
+      <c r="I70" s="15">
         <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
-        <v/>
-      </c>
-      <c r="J70" s="15" t="str">
+        <v>735</v>
+      </c>
+      <c r="J70" s="15">
         <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
-        <v/>
-      </c>
-      <c r="K70" s="16"/>
-      <c r="L70" s="16"/>
-      <c r="M70" s="16"/>
+        <v>705</v>
+      </c>
+      <c r="K70" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L70" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M70" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N70" s="17"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C15796D-79FD-41FA-A83B-3BEA543AA5BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E90AC04D-C84D-4F7C-BEA5-5220EDEE51B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -212,6 +212,9 @@
   </si>
   <si>
     <t>Stressed</t>
+  </si>
+  <si>
+    <t>Satisfied</t>
   </si>
 </sst>
 </file>
@@ -3853,25 +3856,47 @@
       <c r="N70" s="17"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A71" s="13"/>
-      <c r="B71" s="14"/>
-      <c r="C71" s="14"/>
-      <c r="D71" s="14"/>
-      <c r="E71" s="14"/>
-      <c r="F71" s="14"/>
-      <c r="G71" s="14"/>
-      <c r="H71" s="14"/>
-      <c r="I71" s="15" t="str">
+      <c r="A71" s="13">
+        <v>46309</v>
+      </c>
+      <c r="B71" s="14">
+        <v>420</v>
+      </c>
+      <c r="C71" s="14">
+        <v>0</v>
+      </c>
+      <c r="D71" s="14">
+        <v>300</v>
+      </c>
+      <c r="E71" s="14">
+        <v>0</v>
+      </c>
+      <c r="F71" s="14">
+        <v>0</v>
+      </c>
+      <c r="G71" s="14">
+        <v>0</v>
+      </c>
+      <c r="H71" s="14">
+        <v>90</v>
+      </c>
+      <c r="I71" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J71" s="15" t="str">
+        <v>810</v>
+      </c>
+      <c r="J71" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K71" s="16"/>
-      <c r="L71" s="16"/>
-      <c r="M71" s="16"/>
+        <v>630</v>
+      </c>
+      <c r="K71" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L71" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M71" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N71" s="17"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E90AC04D-C84D-4F7C-BEA5-5220EDEE51B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{619EBFE0-360E-491B-A51E-2C981597E879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3900,25 +3900,47 @@
       <c r="N71" s="17"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A72" s="13"/>
-      <c r="B72" s="14"/>
-      <c r="C72" s="14"/>
-      <c r="D72" s="14"/>
-      <c r="E72" s="14"/>
-      <c r="F72" s="14"/>
-      <c r="G72" s="14"/>
-      <c r="H72" s="14"/>
-      <c r="I72" s="15" t="str">
+      <c r="A72" s="13">
+        <v>46310</v>
+      </c>
+      <c r="B72" s="14">
+        <v>420</v>
+      </c>
+      <c r="C72" s="14">
+        <v>0</v>
+      </c>
+      <c r="D72" s="14">
+        <v>300</v>
+      </c>
+      <c r="E72" s="14">
+        <v>0</v>
+      </c>
+      <c r="F72" s="14">
+        <v>0</v>
+      </c>
+      <c r="G72" s="14">
+        <v>0</v>
+      </c>
+      <c r="H72" s="14">
+        <v>90</v>
+      </c>
+      <c r="I72" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J72" s="15" t="str">
+        <v>810</v>
+      </c>
+      <c r="J72" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K72" s="16"/>
-      <c r="L72" s="16"/>
-      <c r="M72" s="16"/>
+        <v>630</v>
+      </c>
+      <c r="K72" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L72" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M72" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N72" s="17"/>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{619EBFE0-360E-491B-A51E-2C981597E879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B221DEB1-06A1-466E-980D-9E254BE0174C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3944,25 +3944,47 @@
       <c r="N72" s="17"/>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A73" s="13"/>
-      <c r="B73" s="14"/>
-      <c r="C73" s="14"/>
-      <c r="D73" s="14"/>
-      <c r="E73" s="14"/>
-      <c r="F73" s="14"/>
-      <c r="G73" s="14"/>
-      <c r="H73" s="14"/>
-      <c r="I73" s="15" t="str">
+      <c r="A73" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B73" s="14">
+        <v>420</v>
+      </c>
+      <c r="C73" s="14">
+        <v>0</v>
+      </c>
+      <c r="D73" s="14">
+        <v>300</v>
+      </c>
+      <c r="E73" s="14">
+        <v>0</v>
+      </c>
+      <c r="F73" s="14">
+        <v>0</v>
+      </c>
+      <c r="G73" s="14">
+        <v>0</v>
+      </c>
+      <c r="H73" s="14">
+        <v>90</v>
+      </c>
+      <c r="I73" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J73" s="15" t="str">
+        <v>810</v>
+      </c>
+      <c r="J73" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K73" s="16"/>
-      <c r="L73" s="16"/>
-      <c r="M73" s="16"/>
+        <v>630</v>
+      </c>
+      <c r="K73" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L73" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M73" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N73" s="17"/>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B221DEB1-06A1-466E-980D-9E254BE0174C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F10789E0-DF56-4989-98EF-D1ED92C28135}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3988,25 +3988,47 @@
       <c r="N73" s="17"/>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A74" s="13"/>
-      <c r="B74" s="14"/>
-      <c r="C74" s="14"/>
-      <c r="D74" s="14"/>
-      <c r="E74" s="14"/>
-      <c r="F74" s="14"/>
-      <c r="G74" s="14"/>
-      <c r="H74" s="14"/>
-      <c r="I74" s="15" t="str">
+      <c r="A74" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B74" s="14">
+        <v>420</v>
+      </c>
+      <c r="C74" s="14">
+        <v>0</v>
+      </c>
+      <c r="D74" s="14">
+        <v>300</v>
+      </c>
+      <c r="E74" s="14">
+        <v>40</v>
+      </c>
+      <c r="F74" s="14">
+        <v>0</v>
+      </c>
+      <c r="G74" s="14">
+        <v>0</v>
+      </c>
+      <c r="H74" s="14">
+        <v>90</v>
+      </c>
+      <c r="I74" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J74" s="15" t="str">
+        <v>850</v>
+      </c>
+      <c r="J74" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K74" s="16"/>
-      <c r="L74" s="16"/>
-      <c r="M74" s="16"/>
+        <v>590</v>
+      </c>
+      <c r="K74" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L74" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M74" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N74" s="17"/>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F10789E0-DF56-4989-98EF-D1ED92C28135}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B4547C7-1842-44BE-A147-4B1A031D16BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4032,25 +4032,47 @@
       <c r="N74" s="17"/>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A75" s="13"/>
-      <c r="B75" s="14"/>
-      <c r="C75" s="14"/>
-      <c r="D75" s="14"/>
-      <c r="E75" s="14"/>
-      <c r="F75" s="14"/>
-      <c r="G75" s="14"/>
-      <c r="H75" s="14"/>
-      <c r="I75" s="15" t="str">
+      <c r="A75" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B75" s="14">
+        <v>420</v>
+      </c>
+      <c r="C75" s="14">
+        <v>0</v>
+      </c>
+      <c r="D75" s="14">
+        <v>240</v>
+      </c>
+      <c r="E75" s="14">
+        <v>40</v>
+      </c>
+      <c r="F75" s="14">
+        <v>0</v>
+      </c>
+      <c r="G75" s="14">
+        <v>0</v>
+      </c>
+      <c r="H75" s="14">
+        <v>90</v>
+      </c>
+      <c r="I75" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J75" s="15" t="str">
+        <v>790</v>
+      </c>
+      <c r="J75" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K75" s="16"/>
-      <c r="L75" s="16"/>
-      <c r="M75" s="16"/>
+        <v>650</v>
+      </c>
+      <c r="K75" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L75" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M75" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N75" s="17"/>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B4547C7-1842-44BE-A147-4B1A031D16BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1230C0D-5F88-4820-8868-567917C924A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4076,25 +4076,47 @@
       <c r="N75" s="17"/>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A76" s="13"/>
-      <c r="B76" s="14"/>
-      <c r="C76" s="14"/>
-      <c r="D76" s="14"/>
-      <c r="E76" s="14"/>
-      <c r="F76" s="14"/>
-      <c r="G76" s="14"/>
-      <c r="H76" s="14"/>
-      <c r="I76" s="15" t="str">
+      <c r="A76" s="13">
+        <v>46314</v>
+      </c>
+      <c r="B76" s="14">
+        <v>420</v>
+      </c>
+      <c r="C76" s="14">
+        <v>0</v>
+      </c>
+      <c r="D76" s="14">
+        <v>180</v>
+      </c>
+      <c r="E76" s="14">
+        <v>30</v>
+      </c>
+      <c r="F76" s="14">
+        <v>250</v>
+      </c>
+      <c r="G76" s="14">
+        <v>5</v>
+      </c>
+      <c r="H76" s="14">
+        <v>90</v>
+      </c>
+      <c r="I76" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J76" s="15" t="str">
+        <v>970</v>
+      </c>
+      <c r="J76" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K76" s="16"/>
-      <c r="L76" s="16"/>
-      <c r="M76" s="16"/>
+        <v>470</v>
+      </c>
+      <c r="K76" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L76" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M76" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N76" s="17"/>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1230C0D-5F88-4820-8868-567917C924A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{745D537C-1062-4CEA-8AD2-4C0F0F83DF19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4120,25 +4120,47 @@
       <c r="N76" s="17"/>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A77" s="13"/>
-      <c r="B77" s="14"/>
-      <c r="C77" s="14"/>
-      <c r="D77" s="14"/>
-      <c r="E77" s="14"/>
-      <c r="F77" s="14"/>
-      <c r="G77" s="14"/>
-      <c r="H77" s="14"/>
-      <c r="I77" s="15" t="str">
+      <c r="A77" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B77" s="14">
+        <v>420</v>
+      </c>
+      <c r="C77" s="14">
+        <v>0</v>
+      </c>
+      <c r="D77" s="14">
+        <v>180</v>
+      </c>
+      <c r="E77" s="14">
+        <v>30</v>
+      </c>
+      <c r="F77" s="14">
+        <v>0</v>
+      </c>
+      <c r="G77" s="14">
+        <v>0</v>
+      </c>
+      <c r="H77" s="14">
+        <v>90</v>
+      </c>
+      <c r="I77" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J77" s="15" t="str">
+        <v>720</v>
+      </c>
+      <c r="J77" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K77" s="16"/>
-      <c r="L77" s="16"/>
-      <c r="M77" s="16"/>
+        <v>720</v>
+      </c>
+      <c r="K77" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L77" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M77" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N77" s="17"/>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{745D537C-1062-4CEA-8AD2-4C0F0F83DF19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57C3612A-3691-4D74-A7BA-5D487D1A09A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4164,25 +4164,47 @@
       <c r="N77" s="17"/>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A78" s="13"/>
-      <c r="B78" s="14"/>
-      <c r="C78" s="14"/>
-      <c r="D78" s="14"/>
-      <c r="E78" s="14"/>
-      <c r="F78" s="14"/>
-      <c r="G78" s="14"/>
-      <c r="H78" s="14"/>
-      <c r="I78" s="15" t="str">
+      <c r="A78" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B78" s="14">
+        <v>420</v>
+      </c>
+      <c r="C78" s="14">
+        <v>0</v>
+      </c>
+      <c r="D78" s="14">
+        <v>180</v>
+      </c>
+      <c r="E78" s="14">
+        <v>30</v>
+      </c>
+      <c r="F78" s="14">
+        <v>300</v>
+      </c>
+      <c r="G78" s="14">
+        <v>6</v>
+      </c>
+      <c r="H78" s="14">
+        <v>90</v>
+      </c>
+      <c r="I78" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J78" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J78" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K78" s="16"/>
-      <c r="L78" s="16"/>
-      <c r="M78" s="16"/>
+        <v>420</v>
+      </c>
+      <c r="K78" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L78" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M78" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="N78" s="17"/>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57C3612A-3691-4D74-A7BA-5D487D1A09A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D1D98DE-5F52-4627-A921-0CDEDED4714A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4208,25 +4208,47 @@
       <c r="N78" s="17"/>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A79" s="13"/>
-      <c r="B79" s="14"/>
-      <c r="C79" s="14"/>
-      <c r="D79" s="14"/>
-      <c r="E79" s="14"/>
-      <c r="F79" s="14"/>
-      <c r="G79" s="14"/>
-      <c r="H79" s="14"/>
-      <c r="I79" s="15" t="str">
+      <c r="A79" s="13">
+        <v>46317</v>
+      </c>
+      <c r="B79" s="14">
+        <v>420</v>
+      </c>
+      <c r="C79" s="14">
+        <v>0</v>
+      </c>
+      <c r="D79" s="14">
+        <v>180</v>
+      </c>
+      <c r="E79" s="14">
+        <v>30</v>
+      </c>
+      <c r="F79" s="14">
+        <v>200</v>
+      </c>
+      <c r="G79" s="14">
+        <v>4</v>
+      </c>
+      <c r="H79" s="14">
+        <v>90</v>
+      </c>
+      <c r="I79" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J79" s="15" t="str">
+        <v>920</v>
+      </c>
+      <c r="J79" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K79" s="16"/>
-      <c r="L79" s="16"/>
-      <c r="M79" s="16"/>
+        <v>520</v>
+      </c>
+      <c r="K79" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L79" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M79" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N79" s="17"/>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D1D98DE-5F52-4627-A921-0CDEDED4714A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6187D74-5F66-4F05-9E57-B7064DEEA52C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4252,25 +4252,47 @@
       <c r="N79" s="17"/>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A80" s="13"/>
-      <c r="B80" s="14"/>
-      <c r="C80" s="14"/>
-      <c r="D80" s="14"/>
-      <c r="E80" s="14"/>
-      <c r="F80" s="14"/>
-      <c r="G80" s="14"/>
-      <c r="H80" s="14"/>
-      <c r="I80" s="15" t="str">
+      <c r="A80" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B80" s="14">
+        <v>420</v>
+      </c>
+      <c r="C80" s="14">
+        <v>0</v>
+      </c>
+      <c r="D80" s="14">
+        <v>180</v>
+      </c>
+      <c r="E80" s="14">
+        <v>40</v>
+      </c>
+      <c r="F80" s="14">
+        <v>250</v>
+      </c>
+      <c r="G80" s="14">
+        <v>5</v>
+      </c>
+      <c r="H80" s="14">
+        <v>90</v>
+      </c>
+      <c r="I80" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J80" s="15" t="str">
+        <v>980</v>
+      </c>
+      <c r="J80" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K80" s="16"/>
-      <c r="L80" s="16"/>
-      <c r="M80" s="16"/>
+        <v>460</v>
+      </c>
+      <c r="K80" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L80" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M80" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N80" s="17"/>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6187D74-5F66-4F05-9E57-B7064DEEA52C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D112031-2193-4CCC-92E7-FBE2ABD1A0BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4296,25 +4296,47 @@
       <c r="N80" s="17"/>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A81" s="13"/>
-      <c r="B81" s="14"/>
-      <c r="C81" s="14"/>
-      <c r="D81" s="14"/>
-      <c r="E81" s="14"/>
-      <c r="F81" s="14"/>
-      <c r="G81" s="14"/>
-      <c r="H81" s="14"/>
-      <c r="I81" s="15" t="str">
+      <c r="A81" s="13">
+        <v>46319</v>
+      </c>
+      <c r="B81" s="14">
+        <v>420</v>
+      </c>
+      <c r="C81" s="14">
+        <v>0</v>
+      </c>
+      <c r="D81" s="14">
+        <v>120</v>
+      </c>
+      <c r="E81" s="14">
+        <v>40</v>
+      </c>
+      <c r="F81" s="14">
+        <v>0</v>
+      </c>
+      <c r="G81" s="14">
+        <v>0</v>
+      </c>
+      <c r="H81" s="14">
+        <v>90</v>
+      </c>
+      <c r="I81" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J81" s="15" t="str">
+        <v>670</v>
+      </c>
+      <c r="J81" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K81" s="16"/>
-      <c r="L81" s="16"/>
-      <c r="M81" s="16"/>
+        <v>770</v>
+      </c>
+      <c r="K81" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L81" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M81" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N81" s="17"/>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D112031-2193-4CCC-92E7-FBE2ABD1A0BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82C912B1-7BCA-477A-B86D-B7905E48FB0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4340,47 +4340,91 @@
       <c r="N81" s="17"/>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A82" s="13"/>
-      <c r="B82" s="14"/>
-      <c r="C82" s="14"/>
-      <c r="D82" s="14"/>
-      <c r="E82" s="14"/>
-      <c r="F82" s="14"/>
-      <c r="G82" s="14"/>
-      <c r="H82" s="14"/>
-      <c r="I82" s="15" t="str">
+      <c r="A82" s="13">
+        <v>46320</v>
+      </c>
+      <c r="B82" s="14">
+        <v>420</v>
+      </c>
+      <c r="C82" s="14">
+        <v>0</v>
+      </c>
+      <c r="D82" s="14">
+        <v>180</v>
+      </c>
+      <c r="E82" s="14">
+        <v>40</v>
+      </c>
+      <c r="F82" s="14">
+        <v>0</v>
+      </c>
+      <c r="G82" s="14">
+        <v>0</v>
+      </c>
+      <c r="H82" s="14">
+        <v>90</v>
+      </c>
+      <c r="I82" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J82" s="15" t="str">
+        <v>730</v>
+      </c>
+      <c r="J82" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K82" s="16"/>
-      <c r="L82" s="16"/>
-      <c r="M82" s="16"/>
+        <v>710</v>
+      </c>
+      <c r="K82" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L82" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M82" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N82" s="17"/>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A83" s="13"/>
-      <c r="B83" s="14"/>
-      <c r="C83" s="14"/>
-      <c r="D83" s="14"/>
-      <c r="E83" s="14"/>
-      <c r="F83" s="14"/>
-      <c r="G83" s="14"/>
-      <c r="H83" s="14"/>
-      <c r="I83" s="15" t="str">
+      <c r="A83" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B83" s="14">
+        <v>420</v>
+      </c>
+      <c r="C83" s="14">
+        <v>0</v>
+      </c>
+      <c r="D83" s="14">
+        <v>180</v>
+      </c>
+      <c r="E83" s="14">
+        <v>40</v>
+      </c>
+      <c r="F83" s="14">
+        <v>0</v>
+      </c>
+      <c r="G83" s="14">
+        <v>0</v>
+      </c>
+      <c r="H83" s="14">
+        <v>90</v>
+      </c>
+      <c r="I83" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J83" s="15" t="str">
+        <v>730</v>
+      </c>
+      <c r="J83" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K83" s="16"/>
-      <c r="L83" s="16"/>
-      <c r="M83" s="16"/>
+        <v>710</v>
+      </c>
+      <c r="K83" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L83" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M83" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N83" s="17"/>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82C912B1-7BCA-477A-B86D-B7905E48FB0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C527814-9B69-47D2-812F-829F6E6C1EB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4428,25 +4428,47 @@
       <c r="N83" s="17"/>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A84" s="13"/>
-      <c r="B84" s="14"/>
-      <c r="C84" s="14"/>
-      <c r="D84" s="14"/>
-      <c r="E84" s="14"/>
-      <c r="F84" s="14"/>
-      <c r="G84" s="14"/>
-      <c r="H84" s="14"/>
-      <c r="I84" s="15" t="str">
+      <c r="A84" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B84" s="14">
+        <v>420</v>
+      </c>
+      <c r="C84" s="14">
+        <v>0</v>
+      </c>
+      <c r="D84" s="14">
+        <v>180</v>
+      </c>
+      <c r="E84" s="14">
+        <v>30</v>
+      </c>
+      <c r="F84" s="14">
+        <v>350</v>
+      </c>
+      <c r="G84" s="14">
+        <v>7</v>
+      </c>
+      <c r="H84" s="14">
+        <v>90</v>
+      </c>
+      <c r="I84" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J84" s="15" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J84" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K84" s="16"/>
-      <c r="L84" s="16"/>
-      <c r="M84" s="16"/>
+        <v>370</v>
+      </c>
+      <c r="K84" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L84" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M84" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N84" s="17"/>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C527814-9B69-47D2-812F-829F6E6C1EB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C5C72D6-BCC6-4E58-BE27-A36431746323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4472,25 +4472,47 @@
       <c r="N84" s="17"/>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A85" s="13"/>
-      <c r="B85" s="14"/>
-      <c r="C85" s="14"/>
-      <c r="D85" s="14"/>
-      <c r="E85" s="14"/>
-      <c r="F85" s="14"/>
-      <c r="G85" s="14"/>
-      <c r="H85" s="14"/>
-      <c r="I85" s="15" t="str">
+      <c r="A85" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B85" s="14">
+        <v>420</v>
+      </c>
+      <c r="C85" s="14">
+        <v>0</v>
+      </c>
+      <c r="D85" s="14">
+        <v>180</v>
+      </c>
+      <c r="E85" s="14">
+        <v>40</v>
+      </c>
+      <c r="F85" s="14">
+        <v>250</v>
+      </c>
+      <c r="G85" s="14">
+        <v>5</v>
+      </c>
+      <c r="H85" s="14">
+        <v>90</v>
+      </c>
+      <c r="I85" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J85" s="15" t="str">
+        <v>980</v>
+      </c>
+      <c r="J85" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K85" s="16"/>
-      <c r="L85" s="16"/>
-      <c r="M85" s="16"/>
+        <v>460</v>
+      </c>
+      <c r="K85" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L85" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M85" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N85" s="17"/>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C5C72D6-BCC6-4E58-BE27-A36431746323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{926FE120-0F7A-4AAC-8BD0-95AB4435A9FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4516,25 +4516,47 @@
       <c r="N85" s="17"/>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A86" s="13"/>
-      <c r="B86" s="14"/>
-      <c r="C86" s="14"/>
-      <c r="D86" s="14"/>
-      <c r="E86" s="14"/>
-      <c r="F86" s="14"/>
-      <c r="G86" s="14"/>
-      <c r="H86" s="14"/>
-      <c r="I86" s="15" t="str">
+      <c r="A86" s="13">
+        <v>46324</v>
+      </c>
+      <c r="B86" s="14">
+        <v>420</v>
+      </c>
+      <c r="C86" s="14">
+        <v>0</v>
+      </c>
+      <c r="D86" s="14">
+        <v>180</v>
+      </c>
+      <c r="E86" s="14">
+        <v>30</v>
+      </c>
+      <c r="F86" s="14">
+        <v>200</v>
+      </c>
+      <c r="G86" s="14">
+        <v>4</v>
+      </c>
+      <c r="H86" s="14">
+        <v>90</v>
+      </c>
+      <c r="I86" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J86" s="15" t="str">
+        <v>920</v>
+      </c>
+      <c r="J86" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K86" s="16"/>
-      <c r="L86" s="16"/>
-      <c r="M86" s="16"/>
+        <v>520</v>
+      </c>
+      <c r="K86" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L86" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M86" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N86" s="17"/>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604704.xlsx
+++ b/12604704.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{926FE120-0F7A-4AAC-8BD0-95AB4435A9FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6145DC3A-31C1-4056-9067-CC44B328DD95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4560,47 +4560,91 @@
       <c r="N86" s="17"/>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A87" s="13"/>
-      <c r="B87" s="14"/>
-      <c r="C87" s="14"/>
-      <c r="D87" s="14"/>
-      <c r="E87" s="14"/>
-      <c r="F87" s="14"/>
-      <c r="G87" s="14"/>
-      <c r="H87" s="14"/>
-      <c r="I87" s="15" t="str">
+      <c r="A87" s="13">
+        <v>46325</v>
+      </c>
+      <c r="B87" s="14">
+        <v>420</v>
+      </c>
+      <c r="C87" s="14">
+        <v>0</v>
+      </c>
+      <c r="D87" s="14">
+        <v>180</v>
+      </c>
+      <c r="E87" s="14">
+        <v>30</v>
+      </c>
+      <c r="F87" s="14">
+        <v>250</v>
+      </c>
+      <c r="G87" s="14">
+        <v>5</v>
+      </c>
+      <c r="H87" s="14">
+        <v>90</v>
+      </c>
+      <c r="I87" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J87" s="15" t="str">
+        <v>970</v>
+      </c>
+      <c r="J87" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K87" s="16"/>
-      <c r="L87" s="16"/>
-      <c r="M87" s="16"/>
+        <v>470</v>
+      </c>
+      <c r="K87" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L87" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M87" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N87" s="17"/>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A88" s="13"/>
-      <c r="B88" s="14"/>
-      <c r="C88" s="14"/>
-      <c r="D88" s="14"/>
-      <c r="E88" s="14"/>
-      <c r="F88" s="14"/>
-      <c r="G88" s="14"/>
-      <c r="H88" s="14"/>
-      <c r="I88" s="15" t="str">
+      <c r="A88" s="13">
+        <v>46326</v>
+      </c>
+      <c r="B88" s="14">
+        <v>420</v>
+      </c>
+      <c r="C88" s="14">
+        <v>0</v>
+      </c>
+      <c r="D88" s="14">
+        <v>240</v>
+      </c>
+      <c r="E88" s="14">
+        <v>40</v>
+      </c>
+      <c r="F88" s="14">
+        <v>0</v>
+      </c>
+      <c r="G88" s="14">
+        <v>0</v>
+      </c>
+      <c r="H88" s="14">
+        <v>90</v>
+      </c>
+      <c r="I88" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J88" s="15" t="str">
+        <v>790</v>
+      </c>
+      <c r="J88" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K88" s="16"/>
-      <c r="L88" s="16"/>
-      <c r="M88" s="16"/>
+        <v>650</v>
+      </c>
+      <c r="K88" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L88" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="M88" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="N88" s="17"/>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.3">
